--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2603_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2603_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO2"/>
+  <dimension ref="A1:BO5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,7 +959,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>Air-Way FF2603 (s32, double-pass 2026-10-15, parts.air-way.com/api/series/32, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p15 FS2603-08-08-08-FG (ORFS-p015-t01); FORGED part: Air-Way NON-forged row FF2603-8-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF2603 (s32, double-pass 2026-10-15, parts.air-way.com/api/series/32, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p15 FS2603-08-08-08-FG (ORFS-p015-t01); FORGED part: Air-Way NON-forged row FF2603-8-8-8-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -970,6 +970,681 @@
       <c r="BO2" t="inlineStr">
         <is>
           <t>FS2603-08-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FS2603-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="F3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="O3" t="n">
+        <v>45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="X3" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0.03383</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>FS2603-06-06-06-FG</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>ORFS Union Tee (male face seal x 3), 11/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (male O-ring face seal, SAE J1453) x 11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>FS2603</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>11/16-16 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>Air-Way FF2603 (s32, double-pass 2026-10-15, parts.air-way.com/api/series/32, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p15 FS2603-06-06-06-FG (ORFS-p015-t01); FORGED part: Air-Way NON-forged row FF2603-6-6-6-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2603-6-6-6-O = Brennan forged FS2603-06-06-06-FG p15 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), M3 LGTH ~ L7 (3), JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2603 is used only where Brennan FS2603-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5404 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>FS2603-06-06-06-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FS2603-10-10-10-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="O4" t="n">
+        <v>45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="X4" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>FS2603-10-10-10-FG</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>ORFS Union Tee (male face seal x 3), 1-14 UN (male O-ring face seal, SAE J1453) x 1-14 UN (male O-ring face seal, SAE J1453) x 1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>FS2603</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>Air-Way FF2603 (s32, double-pass 2026-10-15, parts.air-way.com/api/series/32, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p15 FS2603-10-10-10-FG (ORFS-p015-t01); FORGED part: Air-Way NON-forged row FF2603-10-10-10-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2603-10-10-10-O = Brennan forged FS2603-10-10-10-FG p15 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), M3 LGTH ~ L7 (3), JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2603 is used only where Brennan FS2603-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5407 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>FS2603-10-10-10-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FS2603-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="O5" t="n">
+        <v>45</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="X5" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.4405</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.60775</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>FS2603-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>ORFS Union Tee (male face seal x 3), 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 3/16-12 UN (male O-ring face seal, SAE J1453) x 1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>FS2603</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>1 3/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>Air-Way FF2603 (s32, double-pass 2026-10-15, parts.air-way.com/api/series/32, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p15 FS2603-12-12-12-FG (ORFS-p015-t01); FORGED part: Air-Way NON-forged row FF2603-12-12-12-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF2603-12-12-12-O = Brennan forged FS2603-12-12-12-FG p15 on every compared cell (M1 LGTH ~ L7 (1), M2 LGTH ~ L7 (2), M3 LGTH ~ L7 (3), JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF2603 is used only where Brennan FS2603-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5408 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs)</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>FS2603-12-12-12-FG</t>
         </is>
       </c>
     </row>

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2603_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS2603_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
